--- a/data/trans_orig/P37A$otros-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P37A$otros-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>268268</t>
+          <t>268614</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>529203</t>
+          <t>529463</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6570</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>7539</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>487717</t>
+          <t>486590</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>497379</t>
+          <t>496766</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>988211</t>
+          <t>989485</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>996150</t>
+          <t>996143</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>203302</t>
+          <t>202763</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>406594</t>
+          <t>405990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7879</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>769</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9293</t>
+          <t>8476</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>738068</t>
+          <t>737902</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>775632</t>
+          <t>774913</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1518013</t>
+          <t>1518830</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1526534</t>
+          <t>1526537</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3268128</t>
+          <t>3267704</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3275663</t>
+          <t>3275667</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3369041</t>
+          <t>3368411</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3378211</t>
+          <t>3378213</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6640583</t>
+          <t>6640059</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6651935</t>
+          <t>6652016</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>499456</t>
+          <t>498764</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1022585</t>
+          <t>1023464</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>10379</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10239</t>
+          <t>10135</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>379313</t>
+          <t>378572</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>387927</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>752694</t>
+          <t>752798</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>761917</t>
+          <t>761900</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>687580</t>
+          <t>687666</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1350809</t>
+          <t>1349194</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11884</t>
+          <t>11838</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>15800</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
     </row>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3419291</t>
+          <t>3420023</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3546425</t>
+          <t>3546471</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3556358</t>
+          <t>3556359</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6971069</t>
+          <t>6969288</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6982088</t>
+          <t>6981896</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>7393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>287617</t>
+          <t>287842</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283221</t>
+          <t>283672</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>574410</t>
+          <t>575071</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>495197</t>
+          <t>495224</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1017750</t>
+          <t>1018112</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>873</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>7436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>328499</t>
+          <t>328873</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335420</t>
+          <t>335436</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>647083</t>
+          <t>646946</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653986</t>
+          <t>653992</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>828</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12288</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,47 +8423,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9411</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>883</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9799</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>357676</t>
+          <t>358052</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369119</t>
+          <t>369136</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,49 +8536,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>99,78%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>383840</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>377872</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>386396</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>99,77%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>383840</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>377484</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>386400</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,77%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>706</t>
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>741268</t>
+          <t>741492</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>754685</t>
+          <t>754777</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7248</t>
+          <t>7868</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>8684</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>265867</t>
+          <t>265247</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>529013</t>
+          <t>527554</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10129</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>922</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13867</t>
+          <t>13028</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>646429</t>
+          <t>646441</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>655503</t>
+          <t>655499</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>683334</t>
+          <t>683184</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>690379</t>
+          <t>690372</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1333985</t>
+          <t>1334824</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1344930</t>
+          <t>1345705</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>773252</t>
+          <t>771924</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1599613</t>
+          <t>1598011</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23930</t>
+          <t>23249</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20233</t>
+          <t>20430</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15227</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>36172</t>
+          <t>36591</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3370420</t>
+          <t>3371101</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3387421</t>
+          <t>3387621</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3524309</t>
+          <t>3524112</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3538608</t>
+          <t>3538579</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6902720</t>
+          <t>6902301</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6923665</t>
+          <t>6923742</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>641</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -10742,12 +10742,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>641</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -10777,12 +10777,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -10810,7 +10810,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -10845,27 +10845,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>288970</t>
+          <t>315420</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286254</t>
+          <t>313017</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10880,27 +10880,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>600412</t>
+          <t>634265</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>597671</t>
+          <t>632280</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16219</t>
+          <t>17264</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29409</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20231</t>
+          <t>20382</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>13797</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30286</t>
+          <t>29259</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>36450</t>
+          <t>37646</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26145</t>
+          <t>26904</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51315</t>
+          <t>52349</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>502171</t>
+          <t>513383</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>488981</t>
+          <t>501974</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>510019</t>
+          <t>520850</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>494738</t>
+          <t>526112</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>484683</t>
+          <t>517235</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>501228</t>
+          <t>532697</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>996909</t>
+          <t>1039495</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>982044</t>
+          <t>1024792</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1007214</t>
+          <t>1050237</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -11393,12 +11393,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11428,12 +11428,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,17 +11453,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3111</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>924</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -11496,27 +11496,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>314213</t>
+          <t>314127</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309954</t>
+          <t>309429</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11531,27 +11531,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>347883</t>
+          <t>355136</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>344932</t>
+          <t>351905</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -11566,17 +11566,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>662096</t>
+          <t>669264</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>657356</t>
+          <t>664365</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>664311</t>
+          <t>671451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10512</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12058</t>
+          <t>12537</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17126</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>307991</t>
+          <t>368511</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302352</t>
+          <t>362633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>310908</t>
+          <t>371565</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>470852</t>
+          <t>416793</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>463660</t>
+          <t>409424</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>473966</t>
+          <t>419940</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>778841</t>
+          <t>785305</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>771148</t>
+          <t>776500</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>783726</t>
+          <t>789802</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -12114,12 +12114,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -12217,27 +12217,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>257670</t>
+          <t>227751</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>255020</t>
+          <t>224823</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12252,27 +12252,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>436412</t>
+          <t>433415</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>433067</t>
+          <t>430346</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>648</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,7 +12482,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>648</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -12525,7 +12525,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -12560,17 +12560,17 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>256423</t>
+          <t>263102</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253855</t>
+          <t>259465</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12595,17 +12595,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>526059</t>
+          <t>533809</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>522560</t>
+          <t>531149</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11503</t>
+          <t>13720</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16327</t>
+          <t>21251</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>11180</t>
+          <t>16130</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>9534</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22766</t>
+          <t>29025</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>619180</t>
+          <t>713468</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>612776</t>
+          <t>705967</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>622359</t>
+          <t>717411</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>843184</t>
+          <t>762146</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>832938</t>
+          <t>750806</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>847598</t>
+          <t>767646</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1462364</t>
+          <t>1475614</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1450778</t>
+          <t>1462719</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1467936</t>
+          <t>1482210</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9287</t>
+          <t>10783</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -13178,12 +13178,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>8872</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -13211,27 +13211,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>926143</t>
+          <t>795183</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>919433</t>
+          <t>787289</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -13281,27 +13281,27 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1643875</t>
+          <t>1626514</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1637469</t>
+          <t>1620531</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>30299</t>
+          <t>32872</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19346</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>44262</t>
+          <t>47690</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>34830</t>
+          <t>39162</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24327</t>
+          <t>29078</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47813</t>
+          <t>55356</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>65128</t>
+          <t>72034</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>49201</t>
+          <t>56208</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>84626</t>
+          <t>91698</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3429518</t>
+          <t>3499890</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3415555</t>
+          <t>3485072</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3440471</t>
+          <t>3510718</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3677450</t>
+          <t>3697792</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3664467</t>
+          <t>3681598</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3687953</t>
+          <t>3707876</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>7106969</t>
+          <t>7197682</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7087471</t>
+          <t>7178018</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7122896</t>
+          <t>7213508</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
